--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N102_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N102_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.39565736369888</v>
+        <v>4.289294321601068</v>
       </c>
       <c r="D2" t="n">
-        <v>26.56529994694958</v>
+        <v>4.316861241379307</v>
       </c>
       <c r="E2" t="n">
-        <v>4.645323935487187</v>
+        <v>0.7548651395166679</v>
       </c>
       <c r="F2" t="n">
-        <v>5.358414035388584</v>
+        <v>0.870742280750645</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>16.90824032451586</v>
+        <v>2.747589052733828</v>
       </c>
       <c r="D3" t="n">
-        <v>17.08881788129904</v>
+        <v>2.776932905711094</v>
       </c>
       <c r="E3" t="n">
-        <v>4.645323935487187</v>
+        <v>0.7548651395166679</v>
       </c>
       <c r="F3" t="n">
-        <v>5.358414035388584</v>
+        <v>0.870742280750645</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.21160477973878</v>
+        <v>2.634385776707552</v>
       </c>
       <c r="D4" t="n">
-        <v>13.9623325914558</v>
+        <v>2.268879046111568</v>
       </c>
       <c r="E4" t="n">
-        <v>4.645323935487187</v>
+        <v>0.7548651395166679</v>
       </c>
       <c r="F4" t="n">
-        <v>5.358414035388584</v>
+        <v>0.870742280750645</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
